--- a/MBP_Pipeline_Action_Plan.xlsx
+++ b/MBP_Pipeline_Action_Plan.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Action Plan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Re-Engagement List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Re-Engagement List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Re-Engagement List'!$A$3:$H$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Re-Engagement List'!$A$3:$H$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>83  (28%)</t>
+          <t>79  (27%)</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>43  (15%)</t>
+          <t>47  (16%)</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>39 leads</t>
+          <t>36 leads</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>44 leads</t>
+          <t>43 leads</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -729,7 +729,7 @@
     <row r="20">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>83 warm leads are immediately actionable (see 'Re-Engagement List' tab).</t>
+          <t>79 warm leads are immediately actionable (see 'Re-Engagement List' tab).</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Call/recap the 39 hot + 44 warm leads to close or book.</t>
+          <t>Call/recap the 36 hot + 43 warm leads to close or book.</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H214"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2019,17 +2019,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>SLC Law Office</t>
+          <t>Block Scarpa</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>R Scarpa</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>chris@slclawoffice.com</t>
+          <t>rscarpa@blockscarpa.com</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
@@ -2039,11 +2039,11 @@
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/6/2025</t>
         </is>
       </c>
       <c r="G32" s="16" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
@@ -2059,17 +2059,17 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>Block Scarpa</t>
+          <t>Ali Khan ILaw Offices</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>R Scarpa</t>
+          <t>Saam</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>rscarpa@blockscarpa.com</t>
+          <t>saam@alikhanilawoffices.com</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -2079,11 +2079,11 @@
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>11/6/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="G33" s="16" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
@@ -2099,17 +2099,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Ali Khan ILaw Offices</t>
+          <t>Injury Lawyers Dallas</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>Saam</t>
+          <t>Denny R Martin</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>saam@alikhanilawoffices.com</t>
+          <t>dennyrmartin@injurylawyersdallas</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
@@ -2139,17 +2139,17 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Injury Lawyers Dallas</t>
+          <t>The Barry Law Group</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>Denny R Martin</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>dennyrmartin@injurylawyersdallas</t>
+          <t>ss@thebarrylawgroup.com</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
@@ -2159,11 +2159,11 @@
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/3/2025</t>
         </is>
       </c>
       <c r="G35" s="16" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -2179,17 +2179,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>The Barry Law Group</t>
+          <t>Rozier Legal</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>ss@thebarrylawgroup.com</t>
+          <t>dave@rozierlegal.com</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
@@ -2199,11 +2199,11 @@
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>11/3/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="G36" s="16" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
@@ -2219,17 +2219,17 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>Rozier Legal</t>
+          <t>Stuart Cearley Law</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Stuart</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>dave@rozierlegal.com</t>
+          <t>stuart@stuartcearleylaw.com</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -2239,11 +2239,11 @@
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="G37" s="16" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
@@ -2259,17 +2259,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>Rubio Attorneys</t>
+          <t>Ask For Ory</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>daniel@rubioattorneys.com</t>
+          <t>matt@askforory.com</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
@@ -2279,11 +2279,11 @@
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="G38" s="16" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>Stuart Cearley Law</t>
+          <t>Ocala Injury</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>Stuart</t>
+          <t>William</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>stuart@stuartcearleylaw.com</t>
+          <t>william@ocalainjury.com</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -2319,11 +2319,11 @@
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/24/2025</t>
         </is>
       </c>
       <c r="G39" s="16" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -2332,122 +2332,98 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>1 · Hot</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Ask For Ory</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2 · Warm</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr"/>
+      <c r="C40" s="16" t="inlineStr"/>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>matt@askforory.com</t>
+          <t>info@rajulaw.com</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>4/10/2026</t>
         </is>
       </c>
       <c r="G40" s="16" t="n">
-        <v>232</v>
+        <v>69</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Send recap + proposal; follow up to close</t>
+          <t>Call/email to lock in the meeting they requested</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>1 · Hot</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>Pathlight Legal</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>Tiffany Sams</t>
-        </is>
-      </c>
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>2 · Warm</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr"/>
+      <c r="C41" s="16" t="inlineStr"/>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>tiffanysams@pathlightlegal</t>
+          <t>whf@florinroebig.com</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>3/20/2026</t>
         </is>
       </c>
       <c r="G41" s="16" t="n">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Send recap + proposal; follow up to close</t>
+          <t>Call/email to lock in the meeting they requested</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>1 · Hot</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Ocala Injury</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>William</t>
-        </is>
-      </c>
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2 · Warm</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr"/>
+      <c r="C42" s="16" t="inlineStr"/>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>william@ocalainjury.com</t>
+          <t>closing@lawyer.com</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
         <is>
-          <t>10/24/2025</t>
+          <t>3/20/2026</t>
         </is>
       </c>
       <c r="G42" s="16" t="n">
-        <v>237</v>
+        <v>90</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Send recap + proposal; follow up to close</t>
+          <t>Call/email to lock in the meeting they requested</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2437,7 @@
       <c r="C43" s="16" t="inlineStr"/>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>info@rajulaw.com</t>
+          <t>nolan@awbreylaw.com</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
@@ -2471,11 +2447,11 @@
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>4/10/2026</t>
+          <t>3/18/2026</t>
         </is>
       </c>
       <c r="G43" s="16" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
@@ -2493,7 +2469,7 @@
       <c r="C44" s="16" t="inlineStr"/>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>whf@florinroebig.com</t>
+          <t>kyle@fbtrial.com</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
@@ -2503,11 +2479,11 @@
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>3/20/2026</t>
+          <t>3/17/2026</t>
         </is>
       </c>
       <c r="G44" s="16" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -2525,7 +2501,7 @@
       <c r="C45" s="16" t="inlineStr"/>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>closing@lawyer.com</t>
+          <t>connor@nashlaw.co</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
@@ -2535,11 +2511,11 @@
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>3/20/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="G45" s="16" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -2557,7 +2533,7 @@
       <c r="C46" s="16" t="inlineStr"/>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>nolan@awbreylaw.com</t>
+          <t>karen@petraborgattorneys.com</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
@@ -2567,11 +2543,11 @@
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>3/18/2026</t>
+          <t>3/11/2026</t>
         </is>
       </c>
       <c r="G46" s="16" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
@@ -2589,7 +2565,7 @@
       <c r="C47" s="16" t="inlineStr"/>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>kyle@fbtrial.com</t>
+          <t>jim.standard@stantonlawllc.com</t>
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr">
@@ -2599,11 +2575,11 @@
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>3/17/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="G47" s="16" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
@@ -2621,7 +2597,7 @@
       <c r="C48" s="16" t="inlineStr"/>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>connor@nashlaw.co</t>
+          <t>ron@wekslerlawgroup.com</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
@@ -2631,11 +2607,11 @@
       </c>
       <c r="F48" s="16" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/4/2026</t>
         </is>
       </c>
       <c r="G48" s="16" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
@@ -2653,7 +2629,7 @@
       <c r="C49" s="16" t="inlineStr"/>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>karen@petraborgattorneys.com</t>
+          <t>sunny@myvisasource.com</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr">
@@ -2663,11 +2639,11 @@
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
-          <t>3/11/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="G49" s="16" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
@@ -2681,11 +2657,15 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr"/>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Nest Gen Dental</t>
+        </is>
+      </c>
       <c r="C50" s="16" t="inlineStr"/>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>jim.standard@stantonlawllc.com</t>
+          <t>info@nextgendentalsmiles.com</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
@@ -2695,11 +2675,11 @@
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="G50" s="16" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
@@ -2713,11 +2693,19 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr"/>
-      <c r="C51" s="16" t="inlineStr"/>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Espinoza Law</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>Ruben</t>
+        </is>
+      </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>ron@wekslerlawgroup.com</t>
+          <t>ruben.espinoza@espinozalawgroup.com</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
@@ -2727,11 +2715,11 @@
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>3/4/2026</t>
+          <t>2/18/2026</t>
         </is>
       </c>
       <c r="G51" s="16" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
@@ -2745,11 +2733,15 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr"/>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Trident</t>
+        </is>
+      </c>
       <c r="C52" s="16" t="inlineStr"/>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>sunny@myvisasource.com</t>
+          <t>sa@tridentlegal.com</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
@@ -2759,11 +2751,11 @@
       </c>
       <c r="F52" s="16" t="inlineStr">
         <is>
-          <t>3/2/2026</t>
+          <t>2/9/2026</t>
         </is>
       </c>
       <c r="G52" s="16" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
@@ -2779,13 +2771,17 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>Nest Gen Dental</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr"/>
+          <t>Mccarthy Barnes</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>info@nextgendentalsmiles.com</t>
+          <t>rob@mccarthybarnes.com</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -2795,11 +2791,11 @@
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/8/2026</t>
         </is>
       </c>
       <c r="G53" s="16" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
@@ -2815,17 +2811,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>Espinoza Law</t>
+          <t>MCV Law</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>Ruben</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>ruben.espinoza@espinozalawgroup.com</t>
+          <t>michaelmcv@mamcvicker.com</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
@@ -2835,11 +2831,11 @@
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>2/18/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="G54" s="16" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
@@ -2853,15 +2849,11 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>Trident</t>
-        </is>
-      </c>
+      <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="16" t="inlineStr"/>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>sa@tridentlegal.com</t>
+          <t>asad@lakhani-law.com</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
@@ -2871,11 +2863,11 @@
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>2/9/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="G55" s="16" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
@@ -2891,17 +2883,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>Mccarthy Barnes</t>
+          <t>Solomos Storms</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>rob@mccarthybarnes.com</t>
+          <t>jimmy@solomosstorms.com</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
@@ -2911,11 +2903,11 @@
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>2/8/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="G56" s="16" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
@@ -2929,19 +2921,11 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>MCV Law</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>Michael</t>
-        </is>
-      </c>
+      <c r="B57" s="16" t="inlineStr"/>
+      <c r="C57" s="16" t="inlineStr"/>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>michaelmcv@mamcvicker.com</t>
+          <t>marc@lawciardellicummings.com</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
@@ -2951,11 +2935,11 @@
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="G57" s="16" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
@@ -2969,11 +2953,19 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr"/>
-      <c r="C58" s="16" t="inlineStr"/>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Lindstrom Law Firm</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>asad@lakhani-law.com</t>
+          <t>maya@lindstromlawfirm.com</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
@@ -2983,11 +2975,11 @@
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="G58" s="16" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
@@ -3003,17 +2995,17 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>Solomos Storms</t>
+          <t>DFW Trust and Wills</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Betsy</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>jimmy@solomosstorms.com</t>
+          <t>betsy@dfwtrustandwills.com</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr">
@@ -3023,11 +3015,11 @@
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/5/2026</t>
         </is>
       </c>
       <c r="G59" s="16" t="n">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
@@ -3041,11 +3033,19 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr"/>
-      <c r="C60" s="16" t="inlineStr"/>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>O'Jenian Law</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>Gina</t>
+        </is>
+      </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>marc@lawciardellicummings.com</t>
+          <t>gina@ojenianlaw.com</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
@@ -3055,11 +3055,11 @@
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/5/2026</t>
         </is>
       </c>
       <c r="G60" s="16" t="n">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
@@ -3073,19 +3073,15 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>Wattel and York</t>
-        </is>
-      </c>
+      <c r="B61" s="16" t="inlineStr"/>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Stratton</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>z.hansen@wattelandyork.com</t>
+          <t>stratton@gwu.edu</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
@@ -3095,11 +3091,11 @@
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/1/2026</t>
         </is>
       </c>
       <c r="G61" s="16" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
@@ -3115,17 +3111,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>Lindstrom Law Firm</t>
+          <t>Ricky Bryan</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Ricky Bryan</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>maya@lindstromlawfirm.com</t>
+          <t>rbryan@rickbryan.com</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
@@ -3135,11 +3131,11 @@
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/1/2026</t>
         </is>
       </c>
       <c r="G62" s="16" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
@@ -3155,17 +3151,17 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>DFW Trust and Wills</t>
+          <t>Isso Hughes Law</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>Betsy</t>
+          <t>Ji</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>betsy@dfwtrustandwills.com</t>
+          <t>ji@issohugheslaw.com</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
@@ -3175,11 +3171,11 @@
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>1/5/2026</t>
+          <t>12/21/2025</t>
         </is>
       </c>
       <c r="G63" s="16" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
@@ -3195,17 +3191,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>O'Jenian Law</t>
+          <t>Brock Law Group</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>Gina</t>
+          <t>C Brock</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>gina@ojenianlaw.com</t>
+          <t>cbrock@brocklawgroup.net</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
@@ -3215,11 +3211,11 @@
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>1/5/2026</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="G64" s="16" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
@@ -3233,15 +3229,19 @@
           <t>2 · Warm</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr"/>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>Laiturner Law</t>
+        </is>
+      </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>Stratton</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>stratton@gwu.edu</t>
+          <t>jimmy@laiturnerlaw.com</t>
         </is>
       </c>
       <c r="E65" s="16" t="inlineStr">
@@ -3251,11 +3251,11 @@
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>1/1/2026</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="G65" s="16" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
@@ -3271,17 +3271,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>Ricky Bryan</t>
+          <t>Post Coviction Relief</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>Ricky Bryan</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>rbryan@rickbryan.com</t>
+          <t>info@postconvictionreliefassociates.com</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr">
@@ -3291,11 +3291,11 @@
       </c>
       <c r="F66" s="16" t="inlineStr">
         <is>
-          <t>1/1/2026</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="G66" s="16" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
@@ -3311,17 +3311,17 @@
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>Isso Hughes Law</t>
+          <t>GBP 4 Law</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>Ji</t>
+          <t>George</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>ji@issohugheslaw.com</t>
+          <t>george@gbp4law.com</t>
         </is>
       </c>
       <c r="E67" s="16" t="inlineStr">
@@ -3331,11 +3331,11 @@
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>12/21/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
       <c r="G67" s="16" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
@@ -3351,17 +3351,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>Brock Law Group</t>
+          <t>Scipio Law</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>C Brock</t>
+          <t>darryl</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>cbrock@brocklawgroup.net</t>
+          <t>darryl@scipiolaw.com</t>
         </is>
       </c>
       <c r="E68" s="16" t="inlineStr">
@@ -3371,11 +3371,11 @@
       </c>
       <c r="F68" s="16" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
       <c r="G68" s="16" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
@@ -3391,17 +3391,17 @@
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>Laiturner Law</t>
+          <t>Employee Civil Rights Group</t>
         </is>
       </c>
       <c r="C69" s="16" t="inlineStr">
         <is>
-          <t>jimmy</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>jimmy@laiturnerlaw.com</t>
+          <t>raj@employeecivilrightsgroup.com</t>
         </is>
       </c>
       <c r="E69" s="16" t="inlineStr">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="F69" s="16" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
       <c r="G69" s="16" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
@@ -3431,17 +3431,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>Post Coviction Relief</t>
+          <t>Bergs Law</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>info@postconvictionreliefassociates.com</t>
+          <t>dhenderson@bergslaw.com</t>
         </is>
       </c>
       <c r="E70" s="16" t="inlineStr">
@@ -3451,11 +3451,11 @@
       </c>
       <c r="F70" s="16" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
       <c r="G70" s="16" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
@@ -3471,17 +3471,17 @@
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>GBP 4 Law</t>
+          <t>Mandel &amp; Mandel</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Mike Mandel</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>george@gbp4law.com</t>
+          <t>mike@mandelmandel.com</t>
         </is>
       </c>
       <c r="E71" s="16" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="F71" s="16" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
       <c r="G71" s="16" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
@@ -3511,17 +3511,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>Scipio Law</t>
+          <t>Kintzele Law Group</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>darryl</t>
+          <t>Jonathon Kintzele</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>darryl@scipiolaw.com</t>
+          <t>contact@klawpc.com</t>
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="F72" s="16" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
       <c r="G72" s="16" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
@@ -3551,17 +3551,17 @@
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>Employee Civil Rights Group</t>
+          <t>JP Colgan Law</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>Raj</t>
+          <t>James Colgan</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>raj@employeecivilrightsgroup.com</t>
+          <t>james@jpcolganlaw.com</t>
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr">
@@ -3571,11 +3571,11 @@
       </c>
       <c r="F73" s="16" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
       <c r="G73" s="16" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>Bergs Law</t>
+          <t>Mandell &amp; Mandell</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>dhenderson@bergslaw.com</t>
+          <t>mike@mandelmandel.com</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr">
@@ -3611,11 +3611,11 @@
       </c>
       <c r="F74" s="16" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>12/5/2025</t>
         </is>
       </c>
       <c r="G74" s="16" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
@@ -3631,17 +3631,17 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Mandel &amp; Mandel</t>
+          <t>Ebony Law</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>Mike Mandel</t>
+          <t>Ebony Williams</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>mike@mandelmandel.com</t>
+          <t>ebony@ebonyatlaw.com</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr">
@@ -3651,11 +3651,11 @@
       </c>
       <c r="F75" s="16" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>12/5/2025</t>
         </is>
       </c>
       <c r="G75" s="16" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
@@ -3671,17 +3671,17 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>Kintzele Law Group</t>
+          <t>Mandell Trial Lawyers</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>Jonathon Kintzele</t>
+          <t>Raffi Vartanian</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>contact@klawpc.com</t>
+          <t>raffi@mandelltrial.com</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="F76" s="16" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="G76" s="16" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
@@ -3711,17 +3711,17 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>JP Colgan Law</t>
+          <t>West and West Law</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>James Colgan</t>
+          <t>Jeff West</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>james@jpcolganlaw.com</t>
+          <t>jeff@westandwestlaw.com</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr">
@@ -3731,11 +3731,11 @@
       </c>
       <c r="F77" s="16" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="G77" s="16" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
@@ -3751,17 +3751,17 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>Mandell &amp; Mandell</t>
+          <t>Sargent Law Firm</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Alfonso</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>mike@mandelmandel.com</t>
+          <t>alfonso@sargentlawfirm.com</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr">
@@ -3771,11 +3771,11 @@
       </c>
       <c r="F78" s="16" t="inlineStr">
         <is>
-          <t>12/5/2025</t>
+          <t>11/24/2025</t>
         </is>
       </c>
       <c r="G78" s="16" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
@@ -3791,17 +3791,17 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Ebony Law</t>
+          <t>DC NYC Law</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>Ebony Williams</t>
+          <t>D Cohen</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>ebony@ebonyatlaw.com</t>
+          <t>dcohen@dcnyclaw.com</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr">
@@ -3811,11 +3811,11 @@
       </c>
       <c r="F79" s="16" t="inlineStr">
         <is>
-          <t>12/5/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="G79" s="16" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
@@ -3831,17 +3831,17 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Mandell Trial Lawyers</t>
+          <t>Nava Law LLC</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>Raffi Vartanian</t>
+          <t>J Nava</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>raffi@mandelltrial.com</t>
+          <t>jnava@navalawllc.com</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="F80" s="16" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="G80" s="16" t="n">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
@@ -3871,17 +3871,17 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>West and West Law</t>
+          <t>West Texas Disability Lawyer</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>Jeff West</t>
+          <t>R Fischer</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>jeff@westandwestlaw.com</t>
+          <t>rfischer@westtexasdisabilitylawyer</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr">
@@ -3891,11 +3891,11 @@
       </c>
       <c r="F81" s="16" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="G81" s="16" t="n">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
@@ -3911,17 +3911,17 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>Sargent Law Firm</t>
+          <t>Forrester Lopez</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>Alfonso</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>alfonso@sargentlawfirm.com</t>
+          <t>oscar@forresterlopez.com</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="F82" s="16" t="inlineStr">
         <is>
-          <t>11/24/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="G82" s="16" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
@@ -3944,162 +3944,134 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>2 · Warm</t>
-        </is>
-      </c>
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>DC NYC Law</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>D Cohen</t>
-        </is>
-      </c>
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>3 · Dormant</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="inlineStr"/>
+      <c r="C83" s="16" t="inlineStr"/>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>dcohen@dcnyclaw.com</t>
+          <t>info@vglawfirm.net</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Meeting No Show</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>3/20/2026</t>
         </is>
       </c>
       <c r="G83" s="16" t="n">
-        <v>213</v>
+        <v>90</v>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>Call/email to lock in the meeting they requested</t>
+          <t>Send re-engagement / breakup email — final attempt</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="17" t="inlineStr">
-        <is>
-          <t>2 · Warm</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>Nava Law LLC</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="inlineStr">
-        <is>
-          <t>J Nava</t>
-        </is>
-      </c>
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>3 · Dormant</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr"/>
+      <c r="C84" s="16" t="inlineStr"/>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>jnava@navalawllc.com</t>
+          <t>info@britedentalnyc.com</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Meeting No Show</t>
         </is>
       </c>
       <c r="F84" s="16" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>3/16/2026</t>
         </is>
       </c>
       <c r="G84" s="16" t="n">
-        <v>220</v>
+        <v>94</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>Call/email to lock in the meeting they requested</t>
+          <t>Send re-engagement / breakup email — final attempt</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="17" t="inlineStr">
-        <is>
-          <t>2 · Warm</t>
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>3 · Dormant</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>West Texas Disability Lawyer</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>R Fischer</t>
-        </is>
-      </c>
+          <t>Hurt in Houston</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr"/>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>rfischer@westtexasdisabilitylawyer</t>
+          <t>dsalazar@hurtinhouston.com</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Meeting No Show</t>
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>2/20/2026</t>
         </is>
       </c>
       <c r="G85" s="16" t="n">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>Call/email to lock in the meeting they requested</t>
+          <t>Send re-engagement / breakup email — final attempt</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="17" t="inlineStr">
-        <is>
-          <t>2 · Warm</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="inlineStr">
-        <is>
-          <t>Forrester Lopez</t>
-        </is>
-      </c>
-      <c r="C86" s="16" t="inlineStr">
-        <is>
-          <t>Oscar</t>
-        </is>
-      </c>
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>3 · Dormant</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr"/>
+      <c r="C86" s="16" t="inlineStr"/>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>oscar@forresterlopez.com</t>
+          <t>lora@cjilaw.net</t>
         </is>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Meeting No Show</t>
         </is>
       </c>
       <c r="F86" s="16" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="G86" s="16" t="n">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>Call/email to lock in the meeting they requested</t>
+          <t>Send re-engagement / breakup email — final attempt</t>
         </is>
       </c>
     </row>
@@ -4109,11 +4081,19 @@
           <t>3 · Dormant</t>
         </is>
       </c>
-      <c r="B87" s="16" t="inlineStr"/>
-      <c r="C87" s="16" t="inlineStr"/>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Atom Law</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>Togai</t>
+        </is>
+      </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>info@vglawfirm.net</t>
+          <t>tatac@atom.law</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
@@ -4123,11 +4103,11 @@
       </c>
       <c r="F87" s="16" t="inlineStr">
         <is>
-          <t>3/20/2026</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="G87" s="16" t="n">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
@@ -4141,11 +4121,19 @@
           <t>3 · Dormant</t>
         </is>
       </c>
-      <c r="B88" s="16" t="inlineStr"/>
-      <c r="C88" s="16" t="inlineStr"/>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Franklin Legal</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>J Ballard</t>
+        </is>
+      </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>info@britedentalnyc.com</t>
+          <t>jballard@franklin.legal</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
@@ -4155,11 +4143,11 @@
       </c>
       <c r="F88" s="16" t="inlineStr">
         <is>
-          <t>3/16/2026</t>
+          <t>12/30/2025</t>
         </is>
       </c>
       <c r="G88" s="16" t="n">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
@@ -4175,13 +4163,17 @@
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>Hurt in Houston</t>
-        </is>
-      </c>
-      <c r="C89" s="16" t="inlineStr"/>
+          <t>dasinger defense</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>brian</t>
+        </is>
+      </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>dsalazar@hurtinhouston.com</t>
+          <t>brian@dasingerdefense.com</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
@@ -4191,11 +4183,11 @@
       </c>
       <c r="F89" s="16" t="inlineStr">
         <is>
-          <t>2/20/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G89" s="16" t="n">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
@@ -4209,11 +4201,19 @@
           <t>3 · Dormant</t>
         </is>
       </c>
-      <c r="B90" s="16" t="inlineStr"/>
-      <c r="C90" s="16" t="inlineStr"/>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Ortega Law</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>camilo</t>
+        </is>
+      </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>lora@cjilaw.net</t>
+          <t>camilo@ortega-law.com</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
@@ -4223,11 +4223,11 @@
       </c>
       <c r="F90" s="16" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="G90" s="16" t="n">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>Atom Law</t>
+          <t>brian foley law</t>
         </is>
       </c>
       <c r="C91" s="16" t="inlineStr">
         <is>
-          <t>Togai</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>tatac@atom.law</t>
+          <t>brian@brianjfoleylaw.com</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
@@ -4263,11 +4263,11 @@
       </c>
       <c r="F91" s="16" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="G91" s="16" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
@@ -4281,19 +4281,15 @@
           <t>3 · Dormant</t>
         </is>
       </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>Franklin Legal</t>
-        </is>
-      </c>
+      <c r="B92" s="16" t="inlineStr"/>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>J Ballard</t>
+          <t>Audrey Trigg</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>jballard@franklin.legal</t>
+          <t>atrigg@tglegal.net</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr">
@@ -4303,11 +4299,11 @@
       </c>
       <c r="F92" s="16" t="inlineStr">
         <is>
-          <t>12/30/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
       <c r="G92" s="16" t="n">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
@@ -4323,17 +4319,17 @@
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>dasinger defense</t>
+          <t>Tanner Flomberg</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>brian@dasingerdefense.com</t>
+          <t>owen@tannerflomberg.com</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
@@ -4343,11 +4339,11 @@
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/5/2025</t>
         </is>
       </c>
       <c r="G93" s="16" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
@@ -4363,17 +4359,17 @@
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>Ortega Law</t>
+          <t>Chat Law</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
-          <t>camilo</t>
+          <t>Natalie Ashouri</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>camilo@ortega-law.com</t>
+          <t>natalie@chatlawgroup.com</t>
         </is>
       </c>
       <c r="E94" s="16" t="inlineStr">
@@ -4383,11 +4379,11 @@
       </c>
       <c r="F94" s="16" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="G94" s="16" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
@@ -4403,17 +4399,17 @@
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>brian foley law</t>
+          <t>Bennett Law KY</t>
         </is>
       </c>
       <c r="C95" s="16" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>R Bennett</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>brian@brianjfoleylaw.com</t>
+          <t>rbennett@bennettlawky.com</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr">
@@ -4423,11 +4419,11 @@
       </c>
       <c r="F95" s="16" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>11/24/2025</t>
         </is>
       </c>
       <c r="G95" s="16" t="n">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
@@ -4441,15 +4437,19 @@
           <t>3 · Dormant</t>
         </is>
       </c>
-      <c r="B96" s="16" t="inlineStr"/>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Valenzuela Law</t>
+        </is>
+      </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
-          <t>Audrey Trigg</t>
+          <t>Felix</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>atrigg@tglegal.net</t>
+          <t>felix@valenzuela-law.com</t>
         </is>
       </c>
       <c r="E96" s="16" t="inlineStr">
@@ -4459,11 +4459,11 @@
       </c>
       <c r="F96" s="16" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>11/24/2025</t>
         </is>
       </c>
       <c r="G96" s="16" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
@@ -4479,17 +4479,17 @@
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>Tanner Flomberg</t>
+          <t>Attorney High</t>
         </is>
       </c>
       <c r="C97" s="16" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>owen@tannerflomberg.com</t>
+          <t>curtis@attorneyhigh.com</t>
         </is>
       </c>
       <c r="E97" s="16" t="inlineStr">
@@ -4499,11 +4499,11 @@
       </c>
       <c r="F97" s="16" t="inlineStr">
         <is>
-          <t>12/5/2025</t>
+          <t>11/24/2025</t>
         </is>
       </c>
       <c r="G97" s="16" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
@@ -4519,17 +4519,17 @@
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Chat Law</t>
+          <t>Allen Law Firm</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>Natalie Ashouri</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>natalie@chatlawgroup.com</t>
+          <t>vincent@allenlawfirm.com</t>
         </is>
       </c>
       <c r="E98" s="16" t="inlineStr">
@@ -4539,11 +4539,11 @@
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>11/17/2025</t>
         </is>
       </c>
       <c r="G98" s="16" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
@@ -4559,31 +4559,31 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>Bennett Law KY</t>
+          <t>Lynch Lawyers</t>
         </is>
       </c>
       <c r="C99" s="16" t="inlineStr">
         <is>
-          <t>R Bennett</t>
+          <t>J Bingham</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>rbennett@bennettlawky.com</t>
+          <t>jbingham@lynchlawyers.com</t>
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>Meeting No Show</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F99" s="16" t="inlineStr">
         <is>
-          <t>11/24/2025</t>
+          <t>11/3/2025</t>
         </is>
       </c>
       <c r="G99" s="16" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
@@ -4599,17 +4599,17 @@
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>Valenzuela Law</t>
+          <t>Salah Law Firm</t>
         </is>
       </c>
       <c r="C100" s="16" t="inlineStr">
         <is>
-          <t>Felix</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>felix@valenzuela-law.com</t>
+          <t>info@salahlawfirm.com</t>
         </is>
       </c>
       <c r="E100" s="16" t="inlineStr">
@@ -4619,11 +4619,11 @@
       </c>
       <c r="F100" s="16" t="inlineStr">
         <is>
-          <t>11/24/2025</t>
+          <t>11/3/2025</t>
         </is>
       </c>
       <c r="G100" s="16" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
@@ -4639,31 +4639,31 @@
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>Attorney High</t>
+          <t>Setra Law</t>
         </is>
       </c>
       <c r="C101" s="16" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>curtis@attorneyhigh.com</t>
+          <t>office@setralaw.com</t>
         </is>
       </c>
       <c r="E101" s="16" t="inlineStr">
         <is>
-          <t>Meeting No Show</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
         <is>
-          <t>11/24/2025</t>
+          <t>11/3/2025</t>
         </is>
       </c>
       <c r="G101" s="16" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
@@ -4679,31 +4679,31 @@
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>Allen Law Firm</t>
+          <t>Bramnick Creed</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>E O'Brien</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>vincent@allenlawfirm.com</t>
+          <t>eobrien@bramnickcreed.com</t>
         </is>
       </c>
       <c r="E102" s="16" t="inlineStr">
         <is>
-          <t>Meeting No Show</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F102" s="16" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="G102" s="16" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
@@ -4719,17 +4719,17 @@
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Lynch Lawyers</t>
+          <t>The Carter Firm</t>
         </is>
       </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
-          <t>J Bingham</t>
+          <t>Jed Carter</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>jbingham@lynchlawyers.com</t>
+          <t>jedcarter@thecarterfirm.com</t>
         </is>
       </c>
       <c r="E103" s="16" t="inlineStr">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="F103" s="16" t="inlineStr">
         <is>
-          <t>11/3/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="G103" s="16" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
@@ -4759,31 +4759,31 @@
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>Salah Law Firm</t>
+          <t>Schmidt Ullrich Law</t>
         </is>
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Philipp</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>info@salahlawfirm.com</t>
+          <t>philipp@schmidtullrichlaw.com</t>
         </is>
       </c>
       <c r="E104" s="16" t="inlineStr">
         <is>
-          <t>Meeting No Show</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F104" s="16" t="inlineStr">
         <is>
-          <t>11/3/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="G104" s="16" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
@@ -4799,17 +4799,17 @@
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>Setra Law</t>
+          <t>Amourgis</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Will C</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>office@setralaw.com</t>
+          <t>willc@amourgis.com</t>
         </is>
       </c>
       <c r="E105" s="16" t="inlineStr">
@@ -4819,11 +4819,11 @@
       </c>
       <c r="F105" s="16" t="inlineStr">
         <is>
-          <t>11/3/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="G105" s="16" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
@@ -4839,17 +4839,17 @@
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>Bramnick Creed</t>
+          <t>Fumo Law</t>
         </is>
       </c>
       <c r="C106" s="16" t="inlineStr">
         <is>
-          <t>E O'Brien</t>
+          <t>Ozzie Fumo</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>eobrien@bramnickcreed.com</t>
+          <t>ozzie.fumolaw@gmail.com</t>
         </is>
       </c>
       <c r="E106" s="16" t="inlineStr">
@@ -4859,11 +4859,11 @@
       </c>
       <c r="F106" s="16" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="G106" s="16" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
@@ -4879,17 +4879,17 @@
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>The Carter Firm</t>
+          <t>Milgraum Law</t>
         </is>
       </c>
       <c r="C107" s="16" t="inlineStr">
         <is>
-          <t>Jed Carter</t>
+          <t>Sima</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>jedcarter@thecarterfirm.com</t>
+          <t>sima@milgraumlaw.com</t>
         </is>
       </c>
       <c r="E107" s="16" t="inlineStr">
@@ -4899,11 +4899,11 @@
       </c>
       <c r="F107" s="16" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="G107" s="16" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
@@ -4919,17 +4919,17 @@
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>Schmidt Ullrich Law</t>
+          <t>Kris M Clean Law</t>
         </is>
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t>Philipp</t>
+          <t>Tyson</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>philipp@schmidtullrichlaw.com</t>
+          <t>tyson@krismcleanlaw.com</t>
         </is>
       </c>
       <c r="E108" s="16" t="inlineStr">
@@ -4939,11 +4939,11 @@
       </c>
       <c r="F108" s="16" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="G108" s="16" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>Amourgis</t>
+          <t>Coleman MacDonald</t>
         </is>
       </c>
       <c r="C109" s="16" t="inlineStr">
         <is>
-          <t>Will C</t>
+          <t>D MacDonald</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
         <is>
-          <t>willc@amourgis.com</t>
+          <t>dmacdonald@colemanmacdonald</t>
         </is>
       </c>
       <c r="E109" s="16" t="inlineStr">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="F109" s="16" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="G109" s="16" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
@@ -4999,17 +4999,17 @@
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>Fumo Law</t>
+          <t>J Larsen Law</t>
         </is>
       </c>
       <c r="C110" s="16" t="inlineStr">
         <is>
-          <t>Ozzie Fumo</t>
+          <t>J Larsen</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>ozzie.fumolaw@gmail.com</t>
+          <t>jlarsenlaw@gmail.com</t>
         </is>
       </c>
       <c r="E110" s="16" t="inlineStr">
@@ -5039,17 +5039,17 @@
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>Milgraum Law</t>
+          <t>Anouge Law</t>
         </is>
       </c>
       <c r="C111" s="16" t="inlineStr">
         <is>
-          <t>Sima</t>
+          <t>C Anouge</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>sima@milgraumlaw.com</t>
+          <t>canouge@anougelaw.com</t>
         </is>
       </c>
       <c r="E111" s="16" t="inlineStr">
@@ -5079,17 +5079,17 @@
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>Kris M Clean Law</t>
+          <t>Christensen Hsu Sipes LLP</t>
         </is>
       </c>
       <c r="C112" s="16" t="inlineStr">
         <is>
-          <t>Tyson</t>
+          <t>Renee De Golier</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>tyson@krismcleanlaw.com</t>
+          <t>renee@chs.law</t>
         </is>
       </c>
       <c r="E112" s="16" t="inlineStr">
@@ -5119,31 +5119,31 @@
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>Coleman MacDonald</t>
+          <t>Colemire</t>
         </is>
       </c>
       <c r="C113" s="16" t="inlineStr">
         <is>
-          <t>D MacDonald</t>
+          <t>John</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
         <is>
-          <t>dmacdonald@colemanmacdonald</t>
+          <t>john@colemire.com</t>
         </is>
       </c>
       <c r="E113" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F113" s="16" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/4/2025</t>
         </is>
       </c>
       <c r="G113" s="16" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
@@ -5159,31 +5159,31 @@
       </c>
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>J Larsen Law</t>
+          <t>McElyea Law</t>
         </is>
       </c>
       <c r="C114" s="16" t="inlineStr">
         <is>
-          <t>J Larsen</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>jlarsenlaw@gmail.com</t>
+          <t>tom@mcelyealaw.com</t>
         </is>
       </c>
       <c r="E114" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F114" s="16" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="G114" s="16" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
@@ -5199,31 +5199,31 @@
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>Anouge Law</t>
+          <t>N Rose Law</t>
         </is>
       </c>
       <c r="C115" s="16" t="inlineStr">
         <is>
-          <t>C Anouge</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>canouge@anougelaw.com</t>
+          <t>nicholas@nroselaw.com</t>
         </is>
       </c>
       <c r="E115" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F115" s="16" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="G115" s="16" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
@@ -5239,31 +5239,31 @@
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>Christensen Hsu Sipes LLP</t>
+          <t>Holker Law Offices</t>
         </is>
       </c>
       <c r="C116" s="16" t="inlineStr">
         <is>
-          <t>Renee De Golier</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>renee@chs.law</t>
+          <t>info@holkerlawoffices.com</t>
         </is>
       </c>
       <c r="E116" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F116" s="16" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="G116" s="16" t="n">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
@@ -5279,31 +5279,31 @@
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>Colemire</t>
+          <t>PSN Law Group</t>
         </is>
       </c>
       <c r="C117" s="16" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>john@colemire.com</t>
+          <t>info@psnlawgroup.com</t>
         </is>
       </c>
       <c r="E117" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F117" s="16" t="inlineStr">
         <is>
-          <t>10/4/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="G117" s="16" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
@@ -5319,31 +5319,31 @@
       </c>
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>McElyea Law</t>
+          <t>M Chambers Law</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>tom@mcelyealaw.com</t>
+          <t>michael@mchamberslaw.com</t>
         </is>
       </c>
       <c r="E118" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F118" s="16" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="G118" s="16" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
@@ -5359,31 +5359,31 @@
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>N Rose Law</t>
+          <t>Saejung Lee</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>nicholas@nroselaw.com</t>
+          <t>lee@saejunglee.com</t>
         </is>
       </c>
       <c r="E119" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Meeting No Show</t>
         </is>
       </c>
       <c r="F119" s="16" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="G119" s="16" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
@@ -5399,17 +5399,17 @@
       </c>
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>Holker Law Offices</t>
+          <t>Kozak Law Firm</t>
         </is>
       </c>
       <c r="C120" s="16" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Chuck</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>info@holkerlawoffices.com</t>
+          <t>chuck@kozaklawfirm.com</t>
         </is>
       </c>
       <c r="E120" s="16" t="inlineStr">
@@ -5419,11 +5419,11 @@
       </c>
       <c r="F120" s="16" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/26/2025</t>
         </is>
       </c>
       <c r="G120" s="16" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
@@ -5439,31 +5439,31 @@
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>PSN Law Group</t>
+          <t>Simon Criminal Defense</t>
         </is>
       </c>
       <c r="C121" s="16" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="D121" s="16" t="inlineStr">
         <is>
-          <t>info@psnlawgroup.com</t>
+          <t>joe@simoncriminaldefense.com</t>
         </is>
       </c>
       <c r="E121" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F121" s="16" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/26/2025</t>
         </is>
       </c>
       <c r="G121" s="16" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
@@ -5479,31 +5479,31 @@
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>M Chambers Law</t>
+          <t>Cornell Injury Law</t>
         </is>
       </c>
       <c r="C122" s="16" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>michael@mchamberslaw.com</t>
+          <t>danny@cornellinjurylaw.com</t>
         </is>
       </c>
       <c r="E122" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F122" s="16" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/23/2025</t>
         </is>
       </c>
       <c r="G122" s="16" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
@@ -5519,31 +5519,31 @@
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>Saejung Lee</t>
+          <t>ANM Law Office</t>
         </is>
       </c>
       <c r="C123" s="16" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Aridssa Martinez</t>
         </is>
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>lee@saejunglee.com</t>
+          <t>aridssam@anmlawoffice.com</t>
         </is>
       </c>
       <c r="E123" s="16" t="inlineStr">
         <is>
-          <t>Meeting No Show</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F123" s="16" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="G123" s="16" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
@@ -5559,31 +5559,31 @@
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>Kozak Law Firm</t>
+          <t>Perruzzi Law</t>
         </is>
       </c>
       <c r="C124" s="16" t="inlineStr">
         <is>
-          <t>Chuck</t>
+          <t>C A Perruzzi</t>
         </is>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>chuck@kozaklawfirm.com</t>
+          <t>caperruzzi@perruzzilaw.com</t>
         </is>
       </c>
       <c r="E124" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F124" s="16" t="inlineStr">
         <is>
-          <t>9/26/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="G124" s="16" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
@@ -5599,31 +5599,31 @@
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>Simon Criminal Defense</t>
+          <t>Nicholl Law</t>
         </is>
       </c>
       <c r="C125" s="16" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>J Cusson</t>
         </is>
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>joe@simoncriminaldefense.com</t>
+          <t>jcusson@nicholllaw.com</t>
         </is>
       </c>
       <c r="E125" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F125" s="16" t="inlineStr">
         <is>
-          <t>9/26/2025</t>
+          <t>9/22/2025</t>
         </is>
       </c>
       <c r="G125" s="16" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
@@ -5639,17 +5639,17 @@
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>Cornell Injury Law</t>
+          <t>Vellner Law</t>
         </is>
       </c>
       <c r="C126" s="16" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>danny@cornellinjurylaw.com</t>
+          <t>tony@vellnerlaw.com</t>
         </is>
       </c>
       <c r="E126" s="16" t="inlineStr">
@@ -5659,11 +5659,11 @@
       </c>
       <c r="F126" s="16" t="inlineStr">
         <is>
-          <t>9/23/2025</t>
+          <t>9/19/2025</t>
         </is>
       </c>
       <c r="G126" s="16" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
@@ -5679,17 +5679,17 @@
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>ANM Law Office</t>
+          <t>Josh Tucker Law</t>
         </is>
       </c>
       <c r="C127" s="16" t="inlineStr">
         <is>
-          <t>Aridssa Martinez</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
-          <t>aridssam@anmlawoffice.com</t>
+          <t>sara@joshtuckerlaw.com</t>
         </is>
       </c>
       <c r="E127" s="16" t="inlineStr">
@@ -5699,11 +5699,11 @@
       </c>
       <c r="F127" s="16" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="G127" s="16" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
@@ -5719,17 +5719,17 @@
       </c>
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>Perruzzi Law</t>
+          <t>MBMMW Law</t>
         </is>
       </c>
       <c r="C128" s="16" t="inlineStr">
         <is>
-          <t>C A Perruzzi</t>
+          <t>K Melvin</t>
         </is>
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>caperruzzi@perruzzilaw.com</t>
+          <t>kmelvin@mbmmwlaw.com</t>
         </is>
       </c>
       <c r="E128" s="16" t="inlineStr">
@@ -5739,11 +5739,11 @@
       </c>
       <c r="F128" s="16" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="G128" s="16" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
@@ -5759,17 +5759,17 @@
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>Nicholl Law</t>
+          <t>CB Law Group</t>
         </is>
       </c>
       <c r="C129" s="16" t="inlineStr">
         <is>
-          <t>J Cusson</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="D129" s="16" t="inlineStr">
         <is>
-          <t>jcusson@nicholllaw.com</t>
+          <t>lawyers@cblawgroup.com</t>
         </is>
       </c>
       <c r="E129" s="16" t="inlineStr">
@@ -5779,11 +5779,11 @@
       </c>
       <c r="F129" s="16" t="inlineStr">
         <is>
-          <t>9/22/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="G129" s="16" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
@@ -5799,31 +5799,31 @@
       </c>
       <c r="B130" s="16" t="inlineStr">
         <is>
-          <t>Vellner Law</t>
+          <t>Adam W Law</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>tony@vellnerlaw.com</t>
+          <t>adam@adamwlaw.com</t>
         </is>
       </c>
       <c r="E130" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F130" s="16" t="inlineStr">
         <is>
-          <t>9/19/2025</t>
+          <t>9/18/2025</t>
         </is>
       </c>
       <c r="G130" s="16" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
@@ -5839,22 +5839,22 @@
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Josh Tucker Law</t>
+          <t>Paul Kouri Law</t>
         </is>
       </c>
       <c r="C131" s="16" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="D131" s="16" t="inlineStr">
         <is>
-          <t>sara@joshtuckerlaw.com</t>
+          <t>paul@paulkourilaw.com</t>
         </is>
       </c>
       <c r="E131" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F131" s="16" t="inlineStr">
@@ -5879,17 +5879,17 @@
       </c>
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>MBMMW Law</t>
+          <t>Cahill Esq</t>
         </is>
       </c>
       <c r="C132" s="16" t="inlineStr">
         <is>
-          <t>K Melvin</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="D132" s="16" t="inlineStr">
         <is>
-          <t>kmelvin@mbmmwlaw.com</t>
+          <t>kristen@cahillesq.com</t>
         </is>
       </c>
       <c r="E132" s="16" t="inlineStr">
@@ -5919,17 +5919,17 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>CB Law Group</t>
+          <t>Anton Legal</t>
         </is>
       </c>
       <c r="C133" s="16" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="D133" s="16" t="inlineStr">
         <is>
-          <t>lawyers@cblawgroup.com</t>
+          <t>peter@antonlegal.com</t>
         </is>
       </c>
       <c r="E133" s="16" t="inlineStr">
@@ -5959,17 +5959,17 @@
       </c>
       <c r="B134" s="16" t="inlineStr">
         <is>
-          <t>Adam W Law</t>
+          <t>MT Law Group</t>
         </is>
       </c>
       <c r="C134" s="16" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>A Miller</t>
         </is>
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>adam@adamwlaw.com</t>
+          <t>amiller@mtlawgroup.com</t>
         </is>
       </c>
       <c r="E134" s="16" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Paul Kouri Law</t>
+          <t>JW Law</t>
         </is>
       </c>
       <c r="C135" s="16" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>J Wallace</t>
         </is>
       </c>
       <c r="D135" s="16" t="inlineStr">
         <is>
-          <t>paul@paulkourilaw.com</t>
+          <t>jwallace@jwlaw.pro</t>
         </is>
       </c>
       <c r="E135" s="16" t="inlineStr">
@@ -6039,17 +6039,17 @@
       </c>
       <c r="B136" s="16" t="inlineStr">
         <is>
-          <t>Cahill Esq</t>
+          <t>Pearson Law Firm</t>
         </is>
       </c>
       <c r="C136" s="16" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>Jared</t>
         </is>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>kristen@cahillesq.com</t>
+          <t>jared@pearsonlawfirm.org</t>
         </is>
       </c>
       <c r="E136" s="16" t="inlineStr">
@@ -6079,31 +6079,31 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>Anton Legal</t>
+          <t>NYS Lawyer</t>
         </is>
       </c>
       <c r="C137" s="16" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="D137" s="16" t="inlineStr">
         <is>
-          <t>peter@antonlegal.com</t>
+          <t>brent@nys-lawyer.com</t>
         </is>
       </c>
       <c r="E137" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F137" s="16" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="G137" s="16" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
@@ -6119,31 +6119,31 @@
       </c>
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>MT Law Group</t>
+          <t>Mortlock Law</t>
         </is>
       </c>
       <c r="C138" s="16" t="inlineStr">
         <is>
-          <t>A Miller</t>
+          <t>Bryan</t>
         </is>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>amiller@mtlawgroup.com</t>
+          <t>bryan@mortlocklaw.com</t>
         </is>
       </c>
       <c r="E138" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F138" s="16" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="G138" s="16" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
@@ -6159,31 +6159,31 @@
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>JW Law</t>
+          <t>Ann Toney Law</t>
         </is>
       </c>
       <c r="C139" s="16" t="inlineStr">
         <is>
-          <t>J Wallace</t>
+          <t>Ann Toney</t>
         </is>
       </c>
       <c r="D139" s="16" t="inlineStr">
         <is>
-          <t>jwallace@jwlaw.pro</t>
+          <t>ann@anntoneylaw.com</t>
         </is>
       </c>
       <c r="E139" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F139" s="16" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="G139" s="16" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
@@ -6199,31 +6199,31 @@
       </c>
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>Pearson Law Firm</t>
+          <t>Bonnici Law Group</t>
         </is>
       </c>
       <c r="C140" s="16" t="inlineStr">
         <is>
-          <t>Jared</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>jared@pearsonlawfirm.org</t>
+          <t>josh@bonnicilawgroup.com</t>
         </is>
       </c>
       <c r="E140" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F140" s="16" t="inlineStr">
         <is>
-          <t>9/18/2025</t>
+          <t>9/15/2025</t>
         </is>
       </c>
       <c r="G140" s="16" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
@@ -6239,17 +6239,17 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>NYS Lawyer</t>
+          <t>WAM Lawyers</t>
         </is>
       </c>
       <c r="C141" s="16" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>S Wilcox</t>
         </is>
       </c>
       <c r="D141" s="16" t="inlineStr">
         <is>
-          <t>brent@nys-lawyer.com</t>
+          <t>swilcox@wamlawyers.com</t>
         </is>
       </c>
       <c r="E141" s="16" t="inlineStr">
@@ -6259,11 +6259,11 @@
       </c>
       <c r="F141" s="16" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/11/2025</t>
         </is>
       </c>
       <c r="G141" s="16" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
@@ -6279,31 +6279,31 @@
       </c>
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>Mortlock Law</t>
+          <t>Recorderaser</t>
         </is>
       </c>
       <c r="C142" s="16" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Info</t>
         </is>
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>bryan@mortlocklaw.com</t>
+          <t>info@recorderaser.net</t>
         </is>
       </c>
       <c r="E142" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Meeting No Show</t>
         </is>
       </c>
       <c r="F142" s="16" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/11/2025</t>
         </is>
       </c>
       <c r="G142" s="16" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
@@ -6319,31 +6319,31 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Ann Toney Law</t>
+          <t>Assaf &amp; Siegal</t>
         </is>
       </c>
       <c r="C143" s="16" t="inlineStr">
         <is>
-          <t>Ann Toney</t>
+          <t>M Assaf</t>
         </is>
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>ann@anntoneylaw.com</t>
+          <t>massaf@assafandsiegal.com</t>
         </is>
       </c>
       <c r="E143" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F143" s="16" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/11/2025</t>
         </is>
       </c>
       <c r="G143" s="16" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
@@ -6359,31 +6359,31 @@
       </c>
       <c r="B144" s="16" t="inlineStr">
         <is>
-          <t>Bonnici Law Group</t>
+          <t>Caivano Law</t>
         </is>
       </c>
       <c r="C144" s="16" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>A Caivano</t>
         </is>
       </c>
       <c r="D144" s="16" t="inlineStr">
         <is>
-          <t>josh@bonnicilawgroup.com</t>
+          <t>acaivano@caivanolaw.com</t>
         </is>
       </c>
       <c r="E144" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Meeting No Show</t>
         </is>
       </c>
       <c r="F144" s="16" t="inlineStr">
         <is>
-          <t>9/15/2025</t>
+          <t>9/11/2025</t>
         </is>
       </c>
       <c r="G144" s="16" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
@@ -6399,22 +6399,22 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>WAM Lawyers</t>
+          <t>Adam C. Phillips Lawyer</t>
         </is>
       </c>
       <c r="C145" s="16" t="inlineStr">
         <is>
-          <t>S Wilcox</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>swilcox@wamlawyers.com</t>
+          <t>adam@adamcphillips.lawyer</t>
         </is>
       </c>
       <c r="E145" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F145" s="16" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="B146" s="16" t="inlineStr">
         <is>
-          <t>Recorderaser</t>
+          <t>Chuck Davis Law</t>
         </is>
       </c>
       <c r="C146" s="16" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Ced</t>
         </is>
       </c>
       <c r="D146" s="16" t="inlineStr">
         <is>
-          <t>info@recorderaser.net</t>
+          <t>ced@chuckdavislaw.com</t>
         </is>
       </c>
       <c r="E146" s="16" t="inlineStr">
         <is>
-          <t>Meeting No Show</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F146" s="16" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>Assaf &amp; Siegal</t>
+          <t>S Merritt Law</t>
         </is>
       </c>
       <c r="C147" s="16" t="inlineStr">
         <is>
-          <t>M Assaf</t>
+          <t>Steve M</t>
         </is>
       </c>
       <c r="D147" s="16" t="inlineStr">
         <is>
-          <t>massaf@assafandsiegal.com</t>
+          <t>stevem@smerrittlaw.com</t>
         </is>
       </c>
       <c r="E147" s="16" t="inlineStr">
@@ -6519,22 +6519,22 @@
       </c>
       <c r="B148" s="16" t="inlineStr">
         <is>
-          <t>Caivano Law</t>
+          <t>Supernus Law</t>
         </is>
       </c>
       <c r="C148" s="16" t="inlineStr">
         <is>
-          <t>A Caivano</t>
+          <t>Jed</t>
         </is>
       </c>
       <c r="D148" s="16" t="inlineStr">
         <is>
-          <t>acaivano@caivanolaw.com</t>
+          <t>jed@supernuslaw.com</t>
         </is>
       </c>
       <c r="E148" s="16" t="inlineStr">
         <is>
-          <t>Meeting No Show</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F148" s="16" t="inlineStr">
@@ -6559,17 +6559,17 @@
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Adam C. Phillips Lawyer</t>
+          <t>Conwell Law LLC</t>
         </is>
       </c>
       <c r="C149" s="16" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Gary Conwell</t>
         </is>
       </c>
       <c r="D149" s="16" t="inlineStr">
         <is>
-          <t>adam@adamcphillips.lawyer</t>
+          <t>conwelllawllc@gmail.com</t>
         </is>
       </c>
       <c r="E149" s="16" t="inlineStr">
@@ -6599,31 +6599,31 @@
       </c>
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>Chuck Davis Law</t>
+          <t>Farmer Coker</t>
         </is>
       </c>
       <c r="C150" s="16" t="inlineStr">
         <is>
-          <t>Ced</t>
+          <t>Kcsec</t>
         </is>
       </c>
       <c r="D150" s="16" t="inlineStr">
         <is>
-          <t>ced@chuckdavislaw.com</t>
+          <t>kcsec@farmercoker.com</t>
         </is>
       </c>
       <c r="E150" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F150" s="16" t="inlineStr">
         <is>
-          <t>9/11/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="G150" s="16" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
@@ -6639,31 +6639,31 @@
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>S Merritt Law</t>
+          <t>Ichter Davis</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
         <is>
-          <t>Steve M</t>
+          <t>D Davis</t>
         </is>
       </c>
       <c r="D151" s="16" t="inlineStr">
         <is>
-          <t>stevem@smerrittlaw.com</t>
+          <t>ddavis@ichterdavis.com</t>
         </is>
       </c>
       <c r="E151" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F151" s="16" t="inlineStr">
         <is>
-          <t>9/11/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="G151" s="16" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
@@ -6679,31 +6679,31 @@
       </c>
       <c r="B152" s="16" t="inlineStr">
         <is>
-          <t>Supernus Law</t>
+          <t>Mereces Jeremias</t>
         </is>
       </c>
       <c r="C152" s="16" t="inlineStr">
         <is>
-          <t>Jed</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="D152" s="16" t="inlineStr">
         <is>
-          <t>jed@supernuslaw.com</t>
+          <t>ivan@merecesjeremias.com</t>
         </is>
       </c>
       <c r="E152" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F152" s="16" t="inlineStr">
         <is>
-          <t>9/11/2025</t>
+          <t>9/9/2025</t>
         </is>
       </c>
       <c r="G152" s="16" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
@@ -6719,31 +6719,31 @@
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Conwell Law LLC</t>
+          <t>RTM Law Firm</t>
         </is>
       </c>
       <c r="C153" s="16" t="inlineStr">
         <is>
-          <t>Gary Conwell</t>
+          <t>Hasan</t>
         </is>
       </c>
       <c r="D153" s="16" t="inlineStr">
         <is>
-          <t>conwelllawllc@gmail.com</t>
+          <t>hasan@rtmlawfirm.com</t>
         </is>
       </c>
       <c r="E153" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F153" s="16" t="inlineStr">
         <is>
-          <t>9/11/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="G153" s="16" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
@@ -6759,17 +6759,17 @@
       </c>
       <c r="B154" s="16" t="inlineStr">
         <is>
-          <t>Farmer Coker</t>
+          <t>DeSalvo Law</t>
         </is>
       </c>
       <c r="C154" s="16" t="inlineStr">
         <is>
-          <t>Kcsec</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="D154" s="16" t="inlineStr">
         <is>
-          <t>kcsec@farmercoker.com</t>
+          <t>scott@desalvolaw.com</t>
         </is>
       </c>
       <c r="E154" s="16" t="inlineStr">
@@ -6779,11 +6779,11 @@
       </c>
       <c r="F154" s="16" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="G154" s="16" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
@@ -6799,17 +6799,17 @@
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>Ichter Davis</t>
+          <t>Carney, Rezendes &amp; Crowley</t>
         </is>
       </c>
       <c r="C155" s="16" t="inlineStr">
         <is>
-          <t>D Davis</t>
+          <t>Brendan Carney</t>
         </is>
       </c>
       <c r="D155" s="16" t="inlineStr">
         <is>
-          <t>ddavis@ichterdavis.com</t>
+          <t>brendangcarney@gmail.com</t>
         </is>
       </c>
       <c r="E155" s="16" t="inlineStr">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/8/2025</t>
         </is>
       </c>
       <c r="G155" s="16" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
@@ -6839,17 +6839,17 @@
       </c>
       <c r="B156" s="16" t="inlineStr">
         <is>
-          <t>Mereces Jeremias</t>
+          <t>Injury Attorney</t>
         </is>
       </c>
       <c r="C156" s="16" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Greg Alexander</t>
         </is>
       </c>
       <c r="D156" s="16" t="inlineStr">
         <is>
-          <t>ivan@merecesjeremias.com</t>
+          <t>greg.alexander@injuryattorney.com</t>
         </is>
       </c>
       <c r="E156" s="16" t="inlineStr">
@@ -6859,11 +6859,11 @@
       </c>
       <c r="F156" s="16" t="inlineStr">
         <is>
-          <t>9/9/2025</t>
+          <t>9/4/2025</t>
         </is>
       </c>
       <c r="G156" s="16" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
@@ -6879,17 +6879,17 @@
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>RTM Law Firm</t>
+          <t>PDX Law Group</t>
         </is>
       </c>
       <c r="C157" s="16" t="inlineStr">
         <is>
-          <t>Hasan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="D157" s="16" t="inlineStr">
         <is>
-          <t>hasan@rtmlawfirm.com</t>
+          <t>david@pdxlawgroup.com</t>
         </is>
       </c>
       <c r="E157" s="16" t="inlineStr">
@@ -6899,11 +6899,11 @@
       </c>
       <c r="F157" s="16" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>9/4/2025</t>
         </is>
       </c>
       <c r="G157" s="16" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
@@ -6919,17 +6919,17 @@
       </c>
       <c r="B158" s="16" t="inlineStr">
         <is>
-          <t>DeSalvo Law</t>
+          <t>Hurley Guinn</t>
         </is>
       </c>
       <c r="C158" s="16" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>David</t>
         </is>
       </c>
       <c r="D158" s="16" t="inlineStr">
         <is>
-          <t>scott@desalvolaw.com</t>
+          <t>david@hurleyguinn.com</t>
         </is>
       </c>
       <c r="E158" s="16" t="inlineStr">
@@ -6939,11 +6939,11 @@
       </c>
       <c r="F158" s="16" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>9/3/2025</t>
         </is>
       </c>
       <c r="G158" s="16" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
@@ -6959,31 +6959,31 @@
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>Carney, Rezendes &amp; Crowley</t>
+          <t>Roymna</t>
         </is>
       </c>
       <c r="C159" s="16" t="inlineStr">
         <is>
-          <t>Brendan Carney</t>
+          <t>Glennie</t>
         </is>
       </c>
       <c r="D159" s="16" t="inlineStr">
         <is>
-          <t>brendangcarney@gmail.com</t>
+          <t>glennie@roymna.com</t>
         </is>
       </c>
       <c r="E159" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F159" s="16" t="inlineStr">
         <is>
-          <t>9/8/2025</t>
+          <t>9/3/2025</t>
         </is>
       </c>
       <c r="G159" s="16" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
@@ -6999,31 +6999,31 @@
       </c>
       <c r="B160" s="16" t="inlineStr">
         <is>
-          <t>Injury Attorney</t>
+          <t>Law Marketing Advisors</t>
         </is>
       </c>
       <c r="C160" s="16" t="inlineStr">
         <is>
-          <t>Greg Alexander</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>greg.alexander@injuryattorney.com</t>
+          <t>joel@lawmarketingadvisors.com</t>
         </is>
       </c>
       <c r="E160" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F160" s="16" t="inlineStr">
         <is>
-          <t>9/4/2025</t>
+          <t>9/3/2025</t>
         </is>
       </c>
       <c r="G160" s="16" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
@@ -7039,31 +7039,31 @@
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t>PDX Law Group</t>
+          <t>Elan Law</t>
         </is>
       </c>
       <c r="C161" s="16" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Robert Elan</t>
         </is>
       </c>
       <c r="D161" s="16" t="inlineStr">
         <is>
-          <t>david@pdxlawgroup.com</t>
+          <t>robert.elan@elanlaw.com</t>
         </is>
       </c>
       <c r="E161" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F161" s="16" t="inlineStr">
         <is>
-          <t>9/4/2025</t>
+          <t>9/3/2025</t>
         </is>
       </c>
       <c r="G161" s="16" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
@@ -7079,22 +7079,22 @@
       </c>
       <c r="B162" s="16" t="inlineStr">
         <is>
-          <t>Hurley Guinn</t>
+          <t>Traynor Legal</t>
         </is>
       </c>
       <c r="C162" s="16" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Gerard</t>
         </is>
       </c>
       <c r="D162" s="16" t="inlineStr">
         <is>
-          <t>david@hurleyguinn.com</t>
+          <t>gerard@traynorlegal.com</t>
         </is>
       </c>
       <c r="E162" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F162" s="16" t="inlineStr">
@@ -7119,17 +7119,17 @@
       </c>
       <c r="B163" s="16" t="inlineStr">
         <is>
-          <t>Roymna</t>
+          <t>Patel Law</t>
         </is>
       </c>
       <c r="C163" s="16" t="inlineStr">
         <is>
-          <t>Glennie</t>
+          <t>K Patel</t>
         </is>
       </c>
       <c r="D163" s="16" t="inlineStr">
         <is>
-          <t>glennie@roymna.com</t>
+          <t>kpatel@patel-law.com</t>
         </is>
       </c>
       <c r="E163" s="16" t="inlineStr">
@@ -7159,17 +7159,17 @@
       </c>
       <c r="B164" s="16" t="inlineStr">
         <is>
-          <t>Law Marketing Advisors</t>
+          <t>Angelo Reyes Law</t>
         </is>
       </c>
       <c r="C164" s="16" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="D164" s="16" t="inlineStr">
         <is>
-          <t>joel@lawmarketingadvisors.com</t>
+          <t>angelo@angeloreyeslaw.com</t>
         </is>
       </c>
       <c r="E164" s="16" t="inlineStr">
@@ -7199,17 +7199,17 @@
       </c>
       <c r="B165" s="16" t="inlineStr">
         <is>
-          <t>Elan Law</t>
+          <t>Victor Ashy</t>
         </is>
       </c>
       <c r="C165" s="16" t="inlineStr">
         <is>
-          <t>Robert Elan</t>
+          <t>Victor Ashy</t>
         </is>
       </c>
       <c r="D165" s="16" t="inlineStr">
         <is>
-          <t>robert.elan@elanlaw.com</t>
+          <t>victorashy@victorashy.com</t>
         </is>
       </c>
       <c r="E165" s="16" t="inlineStr">
@@ -7239,17 +7239,17 @@
       </c>
       <c r="B166" s="16" t="inlineStr">
         <is>
-          <t>Traynor Legal</t>
+          <t>Bentley Law Group LLC</t>
         </is>
       </c>
       <c r="C166" s="16" t="inlineStr">
         <is>
-          <t>Gerard</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="D166" s="16" t="inlineStr">
         <is>
-          <t>gerard@traynorlegal.com</t>
+          <t>ian@bentleylawgroupllc.com</t>
         </is>
       </c>
       <c r="E166" s="16" t="inlineStr">
@@ -7279,17 +7279,17 @@
       </c>
       <c r="B167" s="16" t="inlineStr">
         <is>
-          <t>Patel Law</t>
+          <t>Jardine Law</t>
         </is>
       </c>
       <c r="C167" s="16" t="inlineStr">
         <is>
-          <t>K Patel</t>
+          <t>J Campbell</t>
         </is>
       </c>
       <c r="D167" s="16" t="inlineStr">
         <is>
-          <t>kpatel@patel-law.com</t>
+          <t>jcampbell@jardinelaw.com</t>
         </is>
       </c>
       <c r="E167" s="16" t="inlineStr">
@@ -7319,31 +7319,31 @@
       </c>
       <c r="B168" s="16" t="inlineStr">
         <is>
-          <t>Angelo Reyes Law</t>
+          <t>KJT Law Group</t>
         </is>
       </c>
       <c r="C168" s="16" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Arek</t>
         </is>
       </c>
       <c r="D168" s="16" t="inlineStr">
         <is>
-          <t>angelo@angeloreyeslaw.com</t>
+          <t>arek@kjtlawgroup.com</t>
         </is>
       </c>
       <c r="E168" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F168" s="16" t="inlineStr">
         <is>
-          <t>9/3/2025</t>
+          <t>8/29/2025</t>
         </is>
       </c>
       <c r="G168" s="16" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
@@ -7359,31 +7359,31 @@
       </c>
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>Victor Ashy</t>
+          <t>Obrero Law</t>
         </is>
       </c>
       <c r="C169" s="16" t="inlineStr">
         <is>
-          <t>Victor Ashy</t>
+          <t>Sheriff</t>
         </is>
       </c>
       <c r="D169" s="16" t="inlineStr">
         <is>
-          <t>victorashy@victorashy.com</t>
+          <t>sheriff@obrerolaw.com</t>
         </is>
       </c>
       <c r="E169" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
-          <t>9/3/2025</t>
+          <t>8/28/2025</t>
         </is>
       </c>
       <c r="G169" s="16" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
@@ -7399,31 +7399,31 @@
       </c>
       <c r="B170" s="16" t="inlineStr">
         <is>
-          <t>Bentley Law Group LLC</t>
+          <t>Bramblett Legal</t>
         </is>
       </c>
       <c r="C170" s="16" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="D170" s="16" t="inlineStr">
         <is>
-          <t>ian@bentleylawgroupllc.com</t>
+          <t>benny@bramblettlegal.com</t>
         </is>
       </c>
       <c r="E170" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F170" s="16" t="inlineStr">
         <is>
-          <t>9/3/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="G170" s="16" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
@@ -7439,31 +7439,31 @@
       </c>
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>Jardine Law</t>
+          <t>DJG Law Group</t>
         </is>
       </c>
       <c r="C171" s="16" t="inlineStr">
         <is>
-          <t>J Campbell</t>
+          <t>S Jackman</t>
         </is>
       </c>
       <c r="D171" s="16" t="inlineStr">
         <is>
-          <t>jcampbell@jardinelaw.com</t>
+          <t>sjackman@djglawgroup.com</t>
         </is>
       </c>
       <c r="E171" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F171" s="16" t="inlineStr">
         <is>
-          <t>9/3/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="G171" s="16" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
@@ -7479,31 +7479,31 @@
       </c>
       <c r="B172" s="16" t="inlineStr">
         <is>
-          <t>KJT Law Group</t>
+          <t>Serowka Law</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
         <is>
-          <t>Arek</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="D172" s="16" t="inlineStr">
         <is>
-          <t>arek@kjtlawgroup.com</t>
+          <t>ps@serowkalaw.com</t>
         </is>
       </c>
       <c r="E172" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F172" s="16" t="inlineStr">
         <is>
-          <t>8/29/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="G172" s="16" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
@@ -7519,31 +7519,31 @@
       </c>
       <c r="B173" s="16" t="inlineStr">
         <is>
-          <t>Obrero Law</t>
+          <t>Treble Legal</t>
         </is>
       </c>
       <c r="C173" s="16" t="inlineStr">
         <is>
-          <t>Sheriff</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="D173" s="16" t="inlineStr">
         <is>
-          <t>sheriff@obrerolaw.com</t>
+          <t>angela@treblegal.com</t>
         </is>
       </c>
       <c r="E173" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F173" s="16" t="inlineStr">
         <is>
-          <t>8/28/2025</t>
+          <t>8/27/2025</t>
         </is>
       </c>
       <c r="G173" s="16" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
@@ -7559,22 +7559,22 @@
       </c>
       <c r="B174" s="16" t="inlineStr">
         <is>
-          <t>Bramblett Legal</t>
+          <t>Sitake-Wright</t>
         </is>
       </c>
       <c r="C174" s="16" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>Pona</t>
         </is>
       </c>
       <c r="D174" s="16" t="inlineStr">
         <is>
-          <t>benny@bramblettlegal.com</t>
+          <t>pona@sitake-wright.com</t>
         </is>
       </c>
       <c r="E174" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F174" s="16" t="inlineStr">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="B175" s="16" t="inlineStr">
         <is>
-          <t>DJG Law Group</t>
+          <t>Victory Law LLP</t>
         </is>
       </c>
       <c r="C175" s="16" t="inlineStr">
         <is>
-          <t>S Jackman</t>
+          <t>Rastin</t>
         </is>
       </c>
       <c r="D175" s="16" t="inlineStr">
         <is>
-          <t>sjackman@djglawgroup.com</t>
+          <t>rastin@victorylawllp.com</t>
         </is>
       </c>
       <c r="E175" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F175" s="16" t="inlineStr">
@@ -7639,17 +7639,17 @@
       </c>
       <c r="B176" s="16" t="inlineStr">
         <is>
-          <t>Serowka Law</t>
+          <t>Mark Hansen Law</t>
         </is>
       </c>
       <c r="C176" s="16" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>Mark Hansen</t>
         </is>
       </c>
       <c r="D176" s="16" t="inlineStr">
         <is>
-          <t>ps@serowkalaw.com</t>
+          <t>mark@markhansenlaw.com</t>
         </is>
       </c>
       <c r="E176" s="16" t="inlineStr">
@@ -7679,17 +7679,17 @@
       </c>
       <c r="B177" s="16" t="inlineStr">
         <is>
-          <t>Treble Legal</t>
+          <t>Workers Comp Sacto</t>
         </is>
       </c>
       <c r="C177" s="16" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="D177" s="16" t="inlineStr">
         <is>
-          <t>angela@treblegal.com</t>
+          <t>alice@workerscompsacto.com</t>
         </is>
       </c>
       <c r="E177" s="16" t="inlineStr">
@@ -7719,17 +7719,17 @@
       </c>
       <c r="B178" s="16" t="inlineStr">
         <is>
-          <t>Sitake-Wright</t>
+          <t>Lopez DeFilippo</t>
         </is>
       </c>
       <c r="C178" s="16" t="inlineStr">
         <is>
-          <t>Pona</t>
+          <t>Alexander Lopez</t>
         </is>
       </c>
       <c r="D178" s="16" t="inlineStr">
         <is>
-          <t>pona@sitake-wright.com</t>
+          <t>alexanderlopez@lopezdefilippo.com</t>
         </is>
       </c>
       <c r="E178" s="16" t="inlineStr">
@@ -7759,17 +7759,17 @@
       </c>
       <c r="B179" s="16" t="inlineStr">
         <is>
-          <t>Victory Law LLP</t>
+          <t>Gitman Law</t>
         </is>
       </c>
       <c r="C179" s="16" t="inlineStr">
         <is>
-          <t>Rastin</t>
+          <t>Eugene</t>
         </is>
       </c>
       <c r="D179" s="16" t="inlineStr">
         <is>
-          <t>rastin@victorylawllp.com</t>
+          <t>eugene@gitmanlaw.com</t>
         </is>
       </c>
       <c r="E179" s="16" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="B180" s="16" t="inlineStr">
         <is>
-          <t>Mark Hansen Law</t>
+          <t>Justice For Jax</t>
         </is>
       </c>
       <c r="C180" s="16" t="inlineStr">
         <is>
-          <t>Mark Hansen</t>
+          <t>Brett</t>
         </is>
       </c>
       <c r="D180" s="16" t="inlineStr">
         <is>
-          <t>mark@markhansenlaw.com</t>
+          <t>brett@justiceforjax.com</t>
         </is>
       </c>
       <c r="E180" s="16" t="inlineStr">
@@ -7839,17 +7839,17 @@
       </c>
       <c r="B181" s="16" t="inlineStr">
         <is>
-          <t>Workers Comp Sacto</t>
+          <t>McNabola Law</t>
         </is>
       </c>
       <c r="C181" s="16" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="D181" s="16" t="inlineStr">
         <is>
-          <t>alice@workerscompsacto.com</t>
+          <t>don@mcnabolalaw.com</t>
         </is>
       </c>
       <c r="E181" s="16" t="inlineStr">
@@ -7879,31 +7879,31 @@
       </c>
       <c r="B182" s="16" t="inlineStr">
         <is>
-          <t>Lopez DeFilippo</t>
+          <t>Coastal Firm</t>
         </is>
       </c>
       <c r="C182" s="16" t="inlineStr">
         <is>
-          <t>Alexander Lopez</t>
+          <t>Matthew Rubner</t>
         </is>
       </c>
       <c r="D182" s="16" t="inlineStr">
         <is>
-          <t>alexanderlopez@lopezdefilippo.com</t>
+          <t>mrubner@coastalfirm.com</t>
         </is>
       </c>
       <c r="E182" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F182" s="16" t="inlineStr">
         <is>
-          <t>8/27/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="G182" s="16" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
@@ -7919,31 +7919,31 @@
       </c>
       <c r="B183" s="16" t="inlineStr">
         <is>
-          <t>Gitman Law</t>
+          <t>Clemmons Law Firm</t>
         </is>
       </c>
       <c r="C183" s="16" t="inlineStr">
         <is>
-          <t>Eugene</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="D183" s="16" t="inlineStr">
         <is>
-          <t>eugene@gitmanlaw.com</t>
+          <t>doug@clemmonslawfirm.com</t>
         </is>
       </c>
       <c r="E183" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F183" s="16" t="inlineStr">
         <is>
-          <t>8/27/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="G183" s="16" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
@@ -7959,31 +7959,31 @@
       </c>
       <c r="B184" s="16" t="inlineStr">
         <is>
-          <t>Justice For Jax</t>
+          <t>Dickey Law Group</t>
         </is>
       </c>
       <c r="C184" s="16" t="inlineStr">
         <is>
-          <t>Brett</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="D184" s="16" t="inlineStr">
         <is>
-          <t>brett@justiceforjax.com</t>
+          <t>jay@dickeylawgroup.com</t>
         </is>
       </c>
       <c r="E184" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F184" s="16" t="inlineStr">
         <is>
-          <t>8/27/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="G184" s="16" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
@@ -7999,31 +7999,31 @@
       </c>
       <c r="B185" s="16" t="inlineStr">
         <is>
-          <t>McNabola Law</t>
+          <t>Joe Cunningham Law</t>
         </is>
       </c>
       <c r="C185" s="16" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Joe Cunningham</t>
         </is>
       </c>
       <c r="D185" s="16" t="inlineStr">
         <is>
-          <t>don@mcnabolalaw.com</t>
+          <t>joe@joecunninghamlaw.com</t>
         </is>
       </c>
       <c r="E185" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F185" s="16" t="inlineStr">
         <is>
-          <t>8/27/2025</t>
+          <t>8/25/2025</t>
         </is>
       </c>
       <c r="G185" s="16" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
@@ -8039,17 +8039,17 @@
       </c>
       <c r="B186" s="16" t="inlineStr">
         <is>
-          <t>Coastal Firm</t>
+          <t>Rawa Law</t>
         </is>
       </c>
       <c r="C186" s="16" t="inlineStr">
         <is>
-          <t>Matthew Rubner</t>
+          <t>Ziad</t>
         </is>
       </c>
       <c r="D186" s="16" t="inlineStr">
         <is>
-          <t>mrubner@coastalfirm.com</t>
+          <t>ziad@rawalaw.com</t>
         </is>
       </c>
       <c r="E186" s="16" t="inlineStr">
@@ -8059,11 +8059,11 @@
       </c>
       <c r="F186" s="16" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>8/21/2025</t>
         </is>
       </c>
       <c r="G186" s="16" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
@@ -8079,31 +8079,31 @@
       </c>
       <c r="B187" s="16" t="inlineStr">
         <is>
-          <t>Clemmons Law Firm</t>
+          <t>Harry Brown Law</t>
         </is>
       </c>
       <c r="C187" s="16" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Harry Brown</t>
         </is>
       </c>
       <c r="D187" s="16" t="inlineStr">
         <is>
-          <t>doug@clemmonslawfirm.com</t>
+          <t>harry@harrybrownlaw.com</t>
         </is>
       </c>
       <c r="E187" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F187" s="16" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>8/21/2025</t>
         </is>
       </c>
       <c r="G187" s="16" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
@@ -8119,31 +8119,31 @@
       </c>
       <c r="B188" s="16" t="inlineStr">
         <is>
-          <t>Dickey Law Group</t>
+          <t>MB Law</t>
         </is>
       </c>
       <c r="C188" s="16" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="D188" s="16" t="inlineStr">
         <is>
-          <t>jay@dickeylawgroup.com</t>
+          <t>kevin@mblaw.org</t>
         </is>
       </c>
       <c r="E188" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F188" s="16" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>8/21/2025</t>
         </is>
       </c>
       <c r="G188" s="16" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
@@ -8159,31 +8159,31 @@
       </c>
       <c r="B189" s="16" t="inlineStr">
         <is>
-          <t>Joe Cunningham Law</t>
+          <t>Hall Trials</t>
         </is>
       </c>
       <c r="C189" s="16" t="inlineStr">
         <is>
-          <t>Joe Cunningham</t>
+          <t>B Hall</t>
         </is>
       </c>
       <c r="D189" s="16" t="inlineStr">
         <is>
-          <t>joe@joecunninghamlaw.com</t>
+          <t>bhall@halltrials.com</t>
         </is>
       </c>
       <c r="E189" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F189" s="16" t="inlineStr">
         <is>
-          <t>8/25/2025</t>
+          <t>8/21/2025</t>
         </is>
       </c>
       <c r="G189" s="16" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
@@ -8199,22 +8199,22 @@
       </c>
       <c r="B190" s="16" t="inlineStr">
         <is>
-          <t>Rawa Law</t>
+          <t>Rawlings Law</t>
         </is>
       </c>
       <c r="C190" s="16" t="inlineStr">
         <is>
-          <t>Ziad</t>
+          <t>Bill Rawlings</t>
         </is>
       </c>
       <c r="D190" s="16" t="inlineStr">
         <is>
-          <t>ziad@rawalaw.com</t>
+          <t>bill@rawlingslaw.com</t>
         </is>
       </c>
       <c r="E190" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F190" s="16" t="inlineStr">
@@ -8239,17 +8239,17 @@
       </c>
       <c r="B191" s="16" t="inlineStr">
         <is>
-          <t>Harry Brown Law</t>
+          <t>Shield Law APC</t>
         </is>
       </c>
       <c r="C191" s="16" t="inlineStr">
         <is>
-          <t>Harry Brown</t>
+          <t>Kareem</t>
         </is>
       </c>
       <c r="D191" s="16" t="inlineStr">
         <is>
-          <t>harry@harrybrownlaw.com</t>
+          <t>kareem@shieldlawapc.com</t>
         </is>
       </c>
       <c r="E191" s="16" t="inlineStr">
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B192" s="16" t="inlineStr">
         <is>
-          <t>MB Law</t>
+          <t>Zettersten &amp; Hammond</t>
         </is>
       </c>
       <c r="C192" s="16" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Jimmy Zetterstenlaw</t>
         </is>
       </c>
       <c r="D192" s="16" t="inlineStr">
         <is>
-          <t>kevin@mblaw.org</t>
+          <t>jimmy.zetterstenlaw@gmail.com</t>
         </is>
       </c>
       <c r="E192" s="16" t="inlineStr">
@@ -8319,17 +8319,17 @@
       </c>
       <c r="B193" s="16" t="inlineStr">
         <is>
-          <t>Hall Trials</t>
+          <t>Wilshire Law Firm</t>
         </is>
       </c>
       <c r="C193" s="16" t="inlineStr">
         <is>
-          <t>B Hall</t>
+          <t>Marisstella Marinkovic</t>
         </is>
       </c>
       <c r="D193" s="16" t="inlineStr">
         <is>
-          <t>bhall@halltrials.com</t>
+          <t>marisstella.marinkovic@wilshirelawfirm.com</t>
         </is>
       </c>
       <c r="E193" s="16" t="inlineStr">
@@ -8359,17 +8359,17 @@
       </c>
       <c r="B194" s="16" t="inlineStr">
         <is>
-          <t>Rawlings Law</t>
+          <t>Megeredchian Law</t>
         </is>
       </c>
       <c r="C194" s="16" t="inlineStr">
         <is>
-          <t>Bill Rawlings</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="D194" s="16" t="inlineStr">
         <is>
-          <t>bill@rawlingslaw.com</t>
+          <t>alex@megeredchianlaw.com</t>
         </is>
       </c>
       <c r="E194" s="16" t="inlineStr">
@@ -8399,17 +8399,17 @@
       </c>
       <c r="B195" s="16" t="inlineStr">
         <is>
-          <t>Shield Law APC</t>
+          <t>The KD Legal Group</t>
         </is>
       </c>
       <c r="C195" s="16" t="inlineStr">
         <is>
-          <t>Kareem</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D195" s="16" t="inlineStr">
         <is>
-          <t>kareem@shieldlawapc.com</t>
+          <t>jd@thekdlegalgroup.com</t>
         </is>
       </c>
       <c r="E195" s="16" t="inlineStr">
@@ -8439,31 +8439,31 @@
       </c>
       <c r="B196" s="16" t="inlineStr">
         <is>
-          <t>Zettersten &amp; Hammond</t>
+          <t>Ashmore Law</t>
         </is>
       </c>
       <c r="C196" s="16" t="inlineStr">
         <is>
-          <t>Jimmy Zetterstenlaw</t>
+          <t>Gary Ashmore</t>
         </is>
       </c>
       <c r="D196" s="16" t="inlineStr">
         <is>
-          <t>jimmy.zetterstenlaw@gmail.com</t>
+          <t>gashmore@ashmorelaw.com</t>
         </is>
       </c>
       <c r="E196" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F196" s="16" t="inlineStr">
         <is>
-          <t>8/21/2025</t>
+          <t>8/20/2025</t>
         </is>
       </c>
       <c r="G196" s="16" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
@@ -8479,31 +8479,31 @@
       </c>
       <c r="B197" s="16" t="inlineStr">
         <is>
-          <t>Wilshire Law Firm</t>
+          <t>John Ye</t>
         </is>
       </c>
       <c r="C197" s="16" t="inlineStr">
         <is>
-          <t>Marisstella Marinkovic</t>
+          <t>John Ye</t>
         </is>
       </c>
       <c r="D197" s="16" t="inlineStr">
         <is>
-          <t>marisstella.marinkovic@wilshirelawfirm.com</t>
+          <t>jye@johnyelaw.com</t>
         </is>
       </c>
       <c r="E197" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F197" s="16" t="inlineStr">
         <is>
-          <t>8/21/2025</t>
+          <t>8/19/2025</t>
         </is>
       </c>
       <c r="G197" s="16" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
@@ -8519,31 +8519,31 @@
       </c>
       <c r="B198" s="16" t="inlineStr">
         <is>
-          <t>Megeredchian Law</t>
+          <t>Shekter Law</t>
         </is>
       </c>
       <c r="C198" s="16" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Jamison Shekter</t>
         </is>
       </c>
       <c r="D198" s="16" t="inlineStr">
         <is>
-          <t>alex@megeredchianlaw.com</t>
+          <t>jamison@shekterlaw.com</t>
         </is>
       </c>
       <c r="E198" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F198" s="16" t="inlineStr">
         <is>
-          <t>8/21/2025</t>
+          <t>8/19/2025</t>
         </is>
       </c>
       <c r="G198" s="16" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
@@ -8559,31 +8559,31 @@
       </c>
       <c r="B199" s="16" t="inlineStr">
         <is>
-          <t>The KD Legal Group</t>
+          <t>Mamanné Law</t>
         </is>
       </c>
       <c r="C199" s="16" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="D199" s="16" t="inlineStr">
         <is>
-          <t>jd@thekdlegalgroup.com</t>
+          <t>benjamin@mamannelaw.com</t>
         </is>
       </c>
       <c r="E199" s="16" t="inlineStr">
         <is>
-          <t>Interested</t>
+          <t>Had Meeting</t>
         </is>
       </c>
       <c r="F199" s="16" t="inlineStr">
         <is>
-          <t>8/21/2025</t>
+          <t>8/18/2025</t>
         </is>
       </c>
       <c r="G199" s="16" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
@@ -8599,31 +8599,31 @@
       </c>
       <c r="B200" s="16" t="inlineStr">
         <is>
-          <t>Ashmore Law</t>
+          <t>First Gotham</t>
         </is>
       </c>
       <c r="C200" s="16" t="inlineStr">
         <is>
-          <t>Gary Ashmore</t>
+          <t>Pasquale</t>
         </is>
       </c>
       <c r="D200" s="16" t="inlineStr">
         <is>
-          <t>gashmore@ashmorelaw.com</t>
+          <t>pasquale@firstgotham.com</t>
         </is>
       </c>
       <c r="E200" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F200" s="16" t="inlineStr">
         <is>
-          <t>8/20/2025</t>
+          <t>8/14/2025</t>
         </is>
       </c>
       <c r="G200" s="16" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
@@ -8639,31 +8639,31 @@
       </c>
       <c r="B201" s="16" t="inlineStr">
         <is>
-          <t>John Ye</t>
+          <t>Pines Federal</t>
         </is>
       </c>
       <c r="C201" s="16" t="inlineStr">
         <is>
-          <t>John Ye</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="D201" s="16" t="inlineStr">
         <is>
-          <t>jye@johnyelaw.com</t>
+          <t>amanda@pinesfederal.com</t>
         </is>
       </c>
       <c r="E201" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
         <is>
-          <t>8/19/2025</t>
+          <t>8/14/2025</t>
         </is>
       </c>
       <c r="G201" s="16" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
@@ -8679,31 +8679,31 @@
       </c>
       <c r="B202" s="16" t="inlineStr">
         <is>
-          <t>Shekter Law</t>
+          <t>Mahooti Law</t>
         </is>
       </c>
       <c r="C202" s="16" t="inlineStr">
         <is>
-          <t>Jamison Shekter</t>
+          <t>Leila</t>
         </is>
       </c>
       <c r="D202" s="16" t="inlineStr">
         <is>
-          <t>jamison@shekterlaw.com</t>
+          <t>leila@mahootilaw.com</t>
         </is>
       </c>
       <c r="E202" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F202" s="16" t="inlineStr">
         <is>
-          <t>8/19/2025</t>
+          <t>8/14/2025</t>
         </is>
       </c>
       <c r="G202" s="16" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
@@ -8719,31 +8719,31 @@
       </c>
       <c r="B203" s="16" t="inlineStr">
         <is>
-          <t>Mamanné Law</t>
+          <t>CV Injury Law</t>
         </is>
       </c>
       <c r="C203" s="16" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="D203" s="16" t="inlineStr">
         <is>
-          <t>benjamin@mamannelaw.com</t>
+          <t>joe@cvinjurylaw.com</t>
         </is>
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>Had Meeting</t>
+          <t>Interested</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>8/18/2025</t>
+          <t>8/14/2025</t>
         </is>
       </c>
       <c r="G203" s="16" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
@@ -8759,17 +8759,17 @@
       </c>
       <c r="B204" s="16" t="inlineStr">
         <is>
-          <t>First Gotham</t>
+          <t>Ryan McFarland Law</t>
         </is>
       </c>
       <c r="C204" s="16" t="inlineStr">
         <is>
-          <t>Pasquale</t>
+          <t>Ryan McFarland</t>
         </is>
       </c>
       <c r="D204" s="16" t="inlineStr">
         <is>
-          <t>pasquale@firstgotham.com</t>
+          <t>ryan@ryanmcfarlandlaw.com</t>
         </is>
       </c>
       <c r="E204" s="16" t="inlineStr">
@@ -8799,17 +8799,17 @@
       </c>
       <c r="B205" s="16" t="inlineStr">
         <is>
-          <t>Pines Federal</t>
+          <t>Legal Help NM</t>
         </is>
       </c>
       <c r="C205" s="16" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="D205" s="16" t="inlineStr">
         <is>
-          <t>amanda@pinesfederal.com</t>
+          <t>taylor@legalhelpnm.com</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
@@ -8839,17 +8839,17 @@
       </c>
       <c r="B206" s="16" t="inlineStr">
         <is>
-          <t>Mahooti Law</t>
+          <t>Oddo &amp; Babbat</t>
         </is>
       </c>
       <c r="C206" s="16" t="inlineStr">
         <is>
-          <t>Leila</t>
+          <t>David Oddo</t>
         </is>
       </c>
       <c r="D206" s="16" t="inlineStr">
         <is>
-          <t>leila@mahootilaw.com</t>
+          <t>do@oddobabat.com</t>
         </is>
       </c>
       <c r="E206" s="16" t="inlineStr">
@@ -8879,17 +8879,17 @@
       </c>
       <c r="B207" s="16" t="inlineStr">
         <is>
-          <t>CV Injury Law</t>
+          <t>PMC Injury Law</t>
         </is>
       </c>
       <c r="C207" s="16" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="D207" s="16" t="inlineStr">
         <is>
-          <t>joe@cvinjurylaw.com</t>
+          <t>steve@pmcinjurylaw.com</t>
         </is>
       </c>
       <c r="E207" s="16" t="inlineStr">
@@ -8919,17 +8919,17 @@
       </c>
       <c r="B208" s="16" t="inlineStr">
         <is>
-          <t>Ryan McFarland Law</t>
+          <t>Walker Texas Lawyers</t>
         </is>
       </c>
       <c r="C208" s="16" t="inlineStr">
         <is>
-          <t>Ryan McFarland</t>
+          <t>Brad</t>
         </is>
       </c>
       <c r="D208" s="16" t="inlineStr">
         <is>
-          <t>ryan@ryanmcfarlandlaw.com</t>
+          <t>bradwalkertexaslawyer@gmail.com</t>
         </is>
       </c>
       <c r="E208" s="16" t="inlineStr">
@@ -8959,17 +8959,17 @@
       </c>
       <c r="B209" s="16" t="inlineStr">
         <is>
-          <t>Legal Help NM</t>
+          <t>Jacoby &amp; Meyers</t>
         </is>
       </c>
       <c r="C209" s="16" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Tommie Joe</t>
         </is>
       </c>
       <c r="D209" s="16" t="inlineStr">
         <is>
-          <t>taylor@legalhelpnm.com</t>
+          <t>tommieejoe@gmail.com</t>
         </is>
       </c>
       <c r="E209" s="16" t="inlineStr">
@@ -8999,17 +8999,17 @@
       </c>
       <c r="B210" s="16" t="inlineStr">
         <is>
-          <t>Oddo &amp; Babbat</t>
+          <t>Grace Legal Group</t>
         </is>
       </c>
       <c r="C210" s="16" t="inlineStr">
         <is>
-          <t>David Oddo</t>
+          <t>Zino</t>
         </is>
       </c>
       <c r="D210" s="16" t="inlineStr">
         <is>
-          <t>do@oddobabat.com</t>
+          <t>zino@gracelegalgroup.com</t>
         </is>
       </c>
       <c r="E210" s="16" t="inlineStr">
@@ -9031,168 +9031,8 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="18" t="inlineStr">
-        <is>
-          <t>3 · Dormant</t>
-        </is>
-      </c>
-      <c r="B211" s="16" t="inlineStr">
-        <is>
-          <t>PMC Injury Law</t>
-        </is>
-      </c>
-      <c r="C211" s="16" t="inlineStr">
-        <is>
-          <t>Steve</t>
-        </is>
-      </c>
-      <c r="D211" s="16" t="inlineStr">
-        <is>
-          <t>steve@pmcinjurylaw.com</t>
-        </is>
-      </c>
-      <c r="E211" s="16" t="inlineStr">
-        <is>
-          <t>Interested</t>
-        </is>
-      </c>
-      <c r="F211" s="16" t="inlineStr">
-        <is>
-          <t>8/14/2025</t>
-        </is>
-      </c>
-      <c r="G211" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="H211" s="10" t="inlineStr">
-        <is>
-          <t>Send re-engagement / breakup email — final attempt</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="18" t="inlineStr">
-        <is>
-          <t>3 · Dormant</t>
-        </is>
-      </c>
-      <c r="B212" s="16" t="inlineStr">
-        <is>
-          <t>Walker Texas Lawyers</t>
-        </is>
-      </c>
-      <c r="C212" s="16" t="inlineStr">
-        <is>
-          <t>Brad</t>
-        </is>
-      </c>
-      <c r="D212" s="16" t="inlineStr">
-        <is>
-          <t>bradwalkertexaslawyer@gmail.com</t>
-        </is>
-      </c>
-      <c r="E212" s="16" t="inlineStr">
-        <is>
-          <t>Interested</t>
-        </is>
-      </c>
-      <c r="F212" s="16" t="inlineStr">
-        <is>
-          <t>8/14/2025</t>
-        </is>
-      </c>
-      <c r="G212" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="H212" s="10" t="inlineStr">
-        <is>
-          <t>Send re-engagement / breakup email — final attempt</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="18" t="inlineStr">
-        <is>
-          <t>3 · Dormant</t>
-        </is>
-      </c>
-      <c r="B213" s="16" t="inlineStr">
-        <is>
-          <t>Jacoby &amp; Meyers</t>
-        </is>
-      </c>
-      <c r="C213" s="16" t="inlineStr">
-        <is>
-          <t>Tommie Joe</t>
-        </is>
-      </c>
-      <c r="D213" s="16" t="inlineStr">
-        <is>
-          <t>tommieejoe@gmail.com</t>
-        </is>
-      </c>
-      <c r="E213" s="16" t="inlineStr">
-        <is>
-          <t>Interested</t>
-        </is>
-      </c>
-      <c r="F213" s="16" t="inlineStr">
-        <is>
-          <t>8/14/2025</t>
-        </is>
-      </c>
-      <c r="G213" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="H213" s="10" t="inlineStr">
-        <is>
-          <t>Send re-engagement / breakup email — final attempt</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="18" t="inlineStr">
-        <is>
-          <t>3 · Dormant</t>
-        </is>
-      </c>
-      <c r="B214" s="16" t="inlineStr">
-        <is>
-          <t>Grace Legal Group</t>
-        </is>
-      </c>
-      <c r="C214" s="16" t="inlineStr">
-        <is>
-          <t>Zino</t>
-        </is>
-      </c>
-      <c r="D214" s="16" t="inlineStr">
-        <is>
-          <t>zino@gracelegalgroup.com</t>
-        </is>
-      </c>
-      <c r="E214" s="16" t="inlineStr">
-        <is>
-          <t>Interested</t>
-        </is>
-      </c>
-      <c r="F214" s="16" t="inlineStr">
-        <is>
-          <t>8/14/2025</t>
-        </is>
-      </c>
-      <c r="G214" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="H214" s="10" t="inlineStr">
-        <is>
-          <t>Send re-engagement / breakup email — final attempt</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:H214"/>
+  <autoFilter ref="A3:H210"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
